--- a/docs/down-the-rabbit-hole/2026/down-the-rabbit-hole-2026.xlsx
+++ b/docs/down-the-rabbit-hole/2026/down-the-rabbit-hole-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\github\lineup-radar\docs\down-the-rabbit-hole\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CCB25E-F9A8-4970-9985-DB729CCA06D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3364A940-4AAE-4659-A854-8DD5124B7538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{EFF6B510-F57F-4011-AA22-F66678D973A8}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="1902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="1974">
   <si>
     <t>Artist</t>
   </si>
@@ -5728,9 +5728,6 @@
     <t>Ook Belgische nederhop is saai.</t>
   </si>
   <si>
-    <t>Ik vind de plaat leuk (en hem 'm op vinyl).</t>
-  </si>
-  <si>
     <t>Pffff, de Staat van Ontbinding</t>
   </si>
   <si>
@@ -6037,6 +6034,225 @@
   </si>
   <si>
     <t xml:space="preserve">Gezellige Irish-pub folk, niet de spannende Lankum dark-folk variant. "He went into a pub, and came out paralytic". </t>
+  </si>
+  <si>
+    <t>Lekkere slick muziek, jammer dat ie in het Brabants zingt</t>
+  </si>
+  <si>
+    <t>Je laatste kans om ze nog eens te zien</t>
+  </si>
+  <si>
+    <t>Op Lowlands gezien. Twee imposante broers. Luister "Shadowman"!</t>
+  </si>
+  <si>
+    <t>Vrouwen-punk</t>
+  </si>
+  <si>
+    <t>Dutch rapper</t>
+  </si>
+  <si>
+    <t>Mooie vrouw maakt muziek "infused with Arabic influences". Frank gaat natuurlijk kijken.</t>
+  </si>
+  <si>
+    <t>Theaterhater</t>
+  </si>
+  <si>
+    <t>Een beetje te jankerig soms, maar ook mooie Damien Rice-achtige melodieën.</t>
+  </si>
+  <si>
+    <t>Lekkere electo-pop, vijf vrouwen</t>
+  </si>
+  <si>
+    <t>Hun zien er uit als zwarte vrouw en spelen klassiek piano.</t>
+  </si>
+  <si>
+    <t>Verstilde muziek</t>
+  </si>
+  <si>
+    <t>Spinvis zonder de goede muziek.</t>
+  </si>
+  <si>
+    <t>Nog meer muziek uit Afrika met huisvlijt instrumenten</t>
+  </si>
+  <si>
+    <t>Nederhop</t>
+  </si>
+  <si>
+    <t>Strijkkwartet met muziek uit de vorige eeuw.</t>
+  </si>
+  <si>
+    <t>Muziektheater?</t>
+  </si>
+  <si>
+    <t>Retro-soul met een beetje Norah Jones</t>
+  </si>
+  <si>
+    <t>Nederhop, denk ik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lekkere liedjes, lekkere stem. </t>
+  </si>
+  <si>
+    <t>Lekkere grooves, leuke liedjes. On-Duits, meer Bee-Gees meets Whitest Boy Alive.</t>
+  </si>
+  <si>
+    <t>trumpeter creates cosmic deep house</t>
+  </si>
+  <si>
+    <t>DJ producer. Lekkere old-school (87-91) house.</t>
+  </si>
+  <si>
+    <t>Drum-'n-bass</t>
+  </si>
+  <si>
+    <t>Downtempo, moody, Burial, Boards Of Canada</t>
+  </si>
+  <si>
+    <t>Downtempo, moody, vocal samples, spoken word snippets, Boards Of Canada, ja ongeveer net zo als Croatian Amor</t>
+  </si>
+  <si>
+    <t>combining analog synth textures with complex rhythms to create atmospheric soundscapes</t>
+  </si>
+  <si>
+    <t>"His mission is to honor the queer roots of electronic dance music"</t>
+  </si>
+  <si>
+    <t>Engelstalige electro-punk, lekker rommelig en vies</t>
+  </si>
+  <si>
+    <t>Spannende moody post-punk. PJ Harvey.</t>
+  </si>
+  <si>
+    <t>Hiphop met reggaeton.</t>
+  </si>
+  <si>
+    <t>"Stop Met Wenen" is een te gek nummer, rest ook leuk.</t>
+  </si>
+  <si>
+    <t>Matte hardcore</t>
+  </si>
+  <si>
+    <t>Lezing</t>
+  </si>
+  <si>
+    <t>Ik vind de plaat leuk (en heb 'm op vinyl).</t>
+  </si>
+  <si>
+    <t>support act for sisters-in-crime Pussy Riot</t>
+  </si>
+  <si>
+    <t>Nederpunk met humor. "Ik ben een feminist want ik hou ook van kleine tieten". Nou, daar gaat mijn ambitie richting mijn feminist-zijn.</t>
+  </si>
+  <si>
+    <t>Wat zal het zijn? Ik heb geen voorspelling dit jaar.</t>
+  </si>
+  <si>
+    <t>De muziek is een stuk leuker dan de provinciale goth outfits en KISS make-up doen vermoeden. Clan Of Xymox.</t>
+  </si>
+  <si>
+    <t>Hi-energy Korean electronic madness. Breakbeats. Acid.</t>
+  </si>
+  <si>
+    <t>Documentaires</t>
+  </si>
+  <si>
+    <t>"ochtendperformance" van 13:45 - 14:30. "Marokkaanse muziekgenres"</t>
+  </si>
+  <si>
+    <t>Lekkere shoegaze, en ik kan het weten want ik heb ze al in Club Pussycat gezien.</t>
+  </si>
+  <si>
+    <t>High-speed electroclash en punk. Klinkt een beetje geposeerd.</t>
+  </si>
+  <si>
+    <t>Vrouw zingt (soms) over ambient en melancholische muziek. Jon Hopkins. "chill vibes"</t>
+  </si>
+  <si>
+    <t>Bring it on! "dissonant noise, ambient soundscapes, and intricate field recordings"</t>
+  </si>
+  <si>
+    <t>Chipmunks mompel rap over lofi beats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco-born DJ and curator [..] intersectional feminist </t>
+  </si>
+  <si>
+    <t>field recordings</t>
+  </si>
+  <si>
+    <t>a masterful producer with an ear for unconventional textures and more introspective moments, turning his brilliant sets into a kind of meditative listening journey.</t>
+  </si>
+  <si>
+    <t>sometimes with hypnotic meditative sounds, other times with meticulously collected field recordings of humans and nature</t>
+  </si>
+  <si>
+    <t>a Belgian bassist known for her innovative approach to experimental and improvised music, blending elements of noise, jazz, and rock</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>"a haunting blend of neo-ambient, shoegaze, and lo-fi electronica"</t>
+  </si>
+  <si>
+    <t>Intrigerende titels. Spannende muziek. Met zang. Experimental. Electronic.</t>
+  </si>
+  <si>
+    <t>Knutselen</t>
+  </si>
+  <si>
+    <t>Workshop</t>
+  </si>
+  <si>
+    <t>DJ.</t>
+  </si>
+  <si>
+    <t>Vrouw, mexicaans, cumbia!</t>
+  </si>
+  <si>
+    <t>multi-talent from London produces her own tracks</t>
+  </si>
+  <si>
+    <t>Shamaran is een mythisch figuur uit de Noord-Mesopotamische cultuur met de torso van een vrouw en het onderlichaam van twee slangen. Veel gezien in Mardin, Turkije de twee keer dat ik daar was. De DJ heeft "advanced rhythms, razor-sharp percussion, and raw textures"</t>
+  </si>
+  <si>
+    <t>hyperpop</t>
+  </si>
+  <si>
+    <t>a Brazilian live party with musicians gathered around a table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chinnamasta </t>
+  </si>
+  <si>
+    <t>Little Simz' bass player does a DJ set with "Afrohouse, batacuda, and Congolese soukous form the foundation for warm, soulful dance music from the global diaspora, drawing from jazz and old-school funk as well as modern dembow and kuduro"</t>
+  </si>
+  <si>
+    <t>Niche: the only Afro-Indigenous Brazilian female DJ in Europe</t>
+  </si>
+  <si>
+    <t>Woman from Milan plays a "unique fusion of old-school Arabic tunes and global club sounds</t>
+  </si>
+  <si>
+    <t>Contemporary Classical + Experimental</t>
+  </si>
+  <si>
+    <t>"Put That Banger On Next"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DJ </t>
+  </si>
+  <si>
+    <t>Nepo-baby. Yucky is de zoon van Chuckie.</t>
+  </si>
+  <si>
+    <t>Kunst</t>
+  </si>
+  <si>
+    <t>camera obscura</t>
+  </si>
+  <si>
+    <t>...</t>
   </si>
 </sst>
 </file>
@@ -6599,15 +6815,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -6617,6 +6824,15 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -6663,92 +6879,55 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="37">
     <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0" tint="-0.249977111117893"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
@@ -6811,7 +6990,93 @@
       <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6869,49 +7134,52 @@
     <sortCondition ref="A1:A200"/>
   </sortState>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{A2B7DB25-9F02-44A3-92F5-8AC4303F55C6}" uniqueName="1" name="Artist" queryTableFieldId="1" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{09867DA1-6585-4FC0-9022-47F7F8D32952}" uniqueName="2" name="Tagline" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="26" xr3:uid="{AAAA03E8-4844-45C7-9BBF-6D7983E4C3E2}" uniqueName="26" name="My Rating" queryTableFieldId="26" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{A2B7DB25-9F02-44A3-92F5-8AC4303F55C6}" uniqueName="1" name="Artist" queryTableFieldId="1" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{09867DA1-6585-4FC0-9022-47F7F8D32952}" uniqueName="2" name="Tagline" queryTableFieldId="2" dataDxfId="30"/>
+    <tableColumn id="26" xr3:uid="{AAAA03E8-4844-45C7-9BBF-6D7983E4C3E2}" uniqueName="26" name="My Rating" queryTableFieldId="26" dataDxfId="29">
       <calculatedColumnFormula>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{7FD16191-CBB6-4C51-B380-596EE8B18564}" uniqueName="27" name="My Notes" queryTableFieldId="27" dataDxfId="1">
+    <tableColumn id="27" xr3:uid="{7FD16191-CBB6-4C51-B380-596EE8B18564}" uniqueName="27" name="My Notes" queryTableFieldId="27" dataDxfId="28">
       <calculatedColumnFormula>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2F41D7EA-BB80-4CC8-96C6-1757C7550AC2}" uniqueName="3" name="Date" queryTableFieldId="3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{64758273-17A5-4E18-8EE4-8BD792E59740}" uniqueName="4" name="Start Time" queryTableFieldId="4" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{6E39D9CA-BC43-49C8-86B9-D5F3668B9270}" uniqueName="5" name="End Time" queryTableFieldId="5" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{10217C73-CCAB-431B-ADE6-69180AF2092B}" uniqueName="6" name="Stage" queryTableFieldId="6" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{DCCE9C26-B2C7-47DE-A4F3-548049BC5E26}" uniqueName="7" name="Genre" queryTableFieldId="7" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{16964587-597B-47C9-8D2A-B727927D951C}" uniqueName="8" name="Country" queryTableFieldId="8" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{87AD20CC-C89D-48ED-969B-B7B55A658AA8}" uniqueName="9" name="Bio" queryTableFieldId="9" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{CC8ABBB4-81D8-4DD5-8B6A-517E9A2D92E9}" uniqueName="10" name="Website" queryTableFieldId="10" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{24F5BAAE-8BB9-4554-9DB3-08F6ECE1E520}" uniqueName="11" name="Spotify Link" queryTableFieldId="11" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{ADC6DA56-7F1F-4442-BFA3-95416B64ADA4}" uniqueName="12" name="YouTube" queryTableFieldId="12" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{EC7973AC-AB01-4073-B397-6951A09D1718}" uniqueName="13" name="Instagram" queryTableFieldId="13" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{8A7F6CC4-E07B-4165-9971-874EE42A457A}" uniqueName="14" name="AI Summary" queryTableFieldId="14" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{2F41D7EA-BB80-4CC8-96C6-1757C7550AC2}" uniqueName="3" name="Date" queryTableFieldId="3" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{64758273-17A5-4E18-8EE4-8BD792E59740}" uniqueName="4" name="Start Time" queryTableFieldId="4" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{6E39D9CA-BC43-49C8-86B9-D5F3668B9270}" uniqueName="5" name="End Time" queryTableFieldId="5" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{10217C73-CCAB-431B-ADE6-69180AF2092B}" uniqueName="6" name="Stage" queryTableFieldId="6" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{DCCE9C26-B2C7-47DE-A4F3-548049BC5E26}" uniqueName="7" name="Genre" queryTableFieldId="7" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{16964587-597B-47C9-8D2A-B727927D951C}" uniqueName="8" name="Country" queryTableFieldId="8" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{87AD20CC-C89D-48ED-969B-B7B55A658AA8}" uniqueName="9" name="Bio" queryTableFieldId="9" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{CC8ABBB4-81D8-4DD5-8B6A-517E9A2D92E9}" uniqueName="10" name="Website" queryTableFieldId="10" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{24F5BAAE-8BB9-4554-9DB3-08F6ECE1E520}" uniqueName="11" name="Spotify Link" queryTableFieldId="11" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{ADC6DA56-7F1F-4442-BFA3-95416B64ADA4}" uniqueName="12" name="YouTube" queryTableFieldId="12" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{EC7973AC-AB01-4073-B397-6951A09D1718}" uniqueName="13" name="Instagram" queryTableFieldId="13" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{8A7F6CC4-E07B-4165-9971-874EE42A457A}" uniqueName="14" name="AI Summary" queryTableFieldId="14" dataDxfId="16"/>
     <tableColumn id="15" xr3:uid="{BAF90AD5-627D-47AA-9A0B-1CAC8186F1E8}" uniqueName="15" name="AI Rating" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{A04D0901-2B07-48B8-B245-1F4E2450AA60}" uniqueName="16" name="Number of People in Act" queryTableFieldId="16"/>
-    <tableColumn id="17" xr3:uid="{282AFD6B-9962-4394-9976-5D92894BC5BD}" uniqueName="17" name="Gender of Front Person" queryTableFieldId="17" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{528D35E3-81A8-456A-A5B6-B55CAAB009AC}" uniqueName="18" name="Front Person of Color?" queryTableFieldId="18" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{299263B9-E6BA-452D-ABB8-549A79A2BE9B}" uniqueName="19" name="Cancelled" queryTableFieldId="19" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{26E94EE9-0FD9-4A7A-B12F-81A91090DDFD}" uniqueName="20" name="Festival URL" queryTableFieldId="20" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{25F4F4C9-5D03-455A-A2BB-7E207F554CD9}" uniqueName="21" name="Festival Bio (NL)" queryTableFieldId="21" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{AFBB0A8A-FB1D-4606-A672-FBE0CE671A53}" uniqueName="22" name="Festival Bio (EN)" queryTableFieldId="22" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{184FBC33-0427-4C3E-AEE8-7DFB9A7D5A8E}" uniqueName="23" name="Social Links" queryTableFieldId="23" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{3B48047C-48EB-468D-9B3F-3FB765EEA6EE}" uniqueName="24" name="Images Scraped" queryTableFieldId="24" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{4525C30B-1A0D-4111-83AC-8785B6C17334}" uniqueName="25" name="End Date" queryTableFieldId="25" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{282AFD6B-9962-4394-9976-5D92894BC5BD}" uniqueName="17" name="Gender of Front Person" queryTableFieldId="17" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{528D35E3-81A8-456A-A5B6-B55CAAB009AC}" uniqueName="18" name="Front Person of Color?" queryTableFieldId="18" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{299263B9-E6BA-452D-ABB8-549A79A2BE9B}" uniqueName="19" name="Cancelled" queryTableFieldId="19" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{26E94EE9-0FD9-4A7A-B12F-81A91090DDFD}" uniqueName="20" name="Festival URL" queryTableFieldId="20" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{25F4F4C9-5D03-455A-A2BB-7E207F554CD9}" uniqueName="21" name="Festival Bio (NL)" queryTableFieldId="21" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{AFBB0A8A-FB1D-4606-A672-FBE0CE671A53}" uniqueName="22" name="Festival Bio (EN)" queryTableFieldId="22" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{184FBC33-0427-4C3E-AEE8-7DFB9A7D5A8E}" uniqueName="23" name="Social Links" queryTableFieldId="23" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{3B48047C-48EB-468D-9B3F-3FB765EEA6EE}" uniqueName="24" name="Images Scraped" queryTableFieldId="24" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{4525C30B-1A0D-4111-83AC-8785B6C17334}" uniqueName="25" name="End Date" queryTableFieldId="25" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08D80D8F-FDE4-4AB5-88A0-A6F41FE8EB70}" name="Table3" displayName="Table3" ref="A1:C196" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:C196" xr:uid="{08D80D8F-FDE4-4AB5-88A0-A6F41FE8EB70}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08D80D8F-FDE4-4AB5-88A0-A6F41FE8EB70}" name="Table3" displayName="Table3" ref="A1:C195" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:C195" xr:uid="{08D80D8F-FDE4-4AB5-88A0-A6F41FE8EB70}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C195">
+    <sortCondition ref="A1:A195"/>
+  </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6573471A-85CD-4339-B6A7-598BAB0819C4}" name="Artist" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{984FBD7B-8133-4ECF-BFF1-D03697609081}" name="Rating" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{133CC101-D40F-4587-AE0C-7BABC3A349E2}" name="Notes" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{6573471A-85CD-4339-B6A7-598BAB0819C4}" name="Artist" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{984FBD7B-8133-4ECF-BFF1-D03697609081}" name="Rating" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{133CC101-D40F-4587-AE0C-7BABC3A349E2}" name="Notes" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7240,8 +7508,8 @@
   <cols>
     <col min="1" max="1" width="49.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="81.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="81.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -7271,10 +7539,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>1777</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>1778</v>
       </c>
       <c r="E1" t="s">
@@ -7354,11 +7622,11 @@
       <c r="B2" t="s">
         <v>273</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D2" s="15" t="str">
+      <c r="D2" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>DJ. "high-energy sets blending heavy metal, techno, and bass music"</v>
       </c>
@@ -7436,11 +7704,11 @@
       <c r="B3" t="s">
         <v>1229</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Vijf vrouwen - strijkkwartet en saxofoon. Modern piep-knor klassiek.</v>
       </c>
@@ -7518,13 +7786,13 @@
       <c r="B4" t="s">
         <v>742</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D4" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>"Put That Banger On Next"</v>
       </c>
       <c r="E4" s="1">
         <v>46208</v>
@@ -7600,11 +7868,11 @@
       <c r="B5" t="s">
         <v>1259</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D5" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -7618,7 +7886,7 @@
         <v>0.94791666666666663</v>
       </c>
       <c r="H5" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I5" t="s">
         <v>1260</v>
@@ -7679,11 +7947,11 @@
       <c r="B6" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="15" t="str">
+      <c r="D6" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Witte mannen rock-muziek, maar wel spannend. Mogwai-achtige builds.</v>
       </c>
@@ -7764,11 +8032,11 @@
       <c r="B7" t="s">
         <v>546</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D7" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -7849,11 +8117,11 @@
       <c r="B8" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D8" s="15" t="str">
+      <c r="D8" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Warme Duitse electonica met zang</v>
       </c>
@@ -7931,11 +8199,11 @@
       <c r="B9" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D9" s="15" t="str">
+      <c r="D9" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Met een spectaculaire vrouw op de bas. Gezien op Footprints 2024.</v>
       </c>
@@ -8013,11 +8281,11 @@
       <c r="B10" t="s">
         <v>751</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D10" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8095,11 +8363,11 @@
       <c r="B11" t="s">
         <v>555</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D11" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8177,11 +8445,11 @@
       <c r="B12" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D12" s="15" t="str">
+      <c r="D12" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>DJ-set tot 04:30</v>
       </c>
@@ -8259,11 +8527,11 @@
       <c r="B13" t="s">
         <v>757</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D13" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8341,11 +8609,11 @@
       <c r="B14" t="s">
         <v>309</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D14" s="15" t="str">
+      <c r="D14" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Nepo-baby. Allbarone!</v>
       </c>
@@ -8423,11 +8691,11 @@
       <c r="B15" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D15" s="15" t="str">
+      <c r="D15" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Lang niet gezien. Vind het alleen meer iets voor in een tent en 's avonds.</v>
       </c>
@@ -8505,13 +8773,13 @@
       <c r="B16" t="s">
         <v>563</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="15">
+        <v>8</v>
+      </c>
+      <c r="D16" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>DJ producer. Lekkere old-school (87-91) house.</v>
       </c>
       <c r="E16" s="1">
         <v>46206</v>
@@ -8587,11 +8855,11 @@
       <c r="B17" t="s">
         <v>922</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D17" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8608,7 +8876,7 @@
         <v>923</v>
       </c>
       <c r="I17" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="J17" t="s">
         <v>162</v>
@@ -8669,13 +8937,13 @@
       <c r="B18" t="s">
         <v>1061</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="15">
+        <v>5</v>
+      </c>
+      <c r="D18" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Matte hardcore</v>
       </c>
       <c r="E18" s="1">
         <v>46208</v>
@@ -8748,11 +9016,11 @@
       <c r="B19" t="s">
         <v>766</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D19" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8830,13 +9098,13 @@
       <c r="B20" t="s">
         <v>572</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D20" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>"His mission is to honor the queer roots of electronic dance music"</v>
       </c>
       <c r="E20" s="1">
         <v>46209</v>
@@ -8851,7 +9119,7 @@
         <v>547</v>
       </c>
       <c r="I20" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="J20" t="s">
         <v>113</v>
@@ -8912,11 +9180,11 @@
       <c r="B21" t="s">
         <v>772</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D21" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -8994,11 +9262,11 @@
       <c r="B22" t="s">
         <v>930</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D22" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -9073,11 +9341,11 @@
       <c r="B23" t="s">
         <v>318</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D23" s="15" t="str">
+      <c r="D23" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Frans-Canadese pop-zangeres</v>
       </c>
@@ -9150,16 +9418,16 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B24" t="s">
         <v>1874</v>
       </c>
-      <c r="B24" t="s">
-        <v>1875</v>
-      </c>
-      <c r="C24" s="12" t="str">
+      <c r="C24" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v/>
       </c>
-      <c r="D24" s="15" t="str">
+      <c r="D24" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v/>
       </c>
@@ -9176,28 +9444,28 @@
         <v>743</v>
       </c>
       <c r="I24" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="J24" t="s">
         <v>162</v>
       </c>
       <c r="K24" t="s">
+        <v>1876</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1395</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N24" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O24" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P24" t="s">
         <v>1877</v>
-      </c>
-      <c r="L24" t="s">
-        <v>1395</v>
-      </c>
-      <c r="M24" t="s">
-        <v>1859</v>
-      </c>
-      <c r="N24" t="s">
-        <v>1395</v>
-      </c>
-      <c r="O24" t="s">
-        <v>1395</v>
-      </c>
-      <c r="P24" t="s">
-        <v>1878</v>
       </c>
       <c r="Q24">
         <v>6</v>
@@ -9212,16 +9480,16 @@
         <v>1395</v>
       </c>
       <c r="V24" t="s">
+        <v>1878</v>
+      </c>
+      <c r="W24" t="s">
         <v>1879</v>
       </c>
-      <c r="W24" t="s">
+      <c r="X24" t="s">
         <v>1880</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>1881</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>1882</v>
       </c>
       <c r="Z24" t="s">
         <v>38</v>
@@ -9237,11 +9505,11 @@
       <c r="B25" t="s">
         <v>580</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D25" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -9319,13 +9587,13 @@
       <c r="B26" t="s">
         <v>328</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="15">
+        <v>7</v>
+      </c>
+      <c r="D26" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Je laatste kans om ze nog eens te zien</v>
       </c>
       <c r="E26" s="1">
         <v>46208</v>
@@ -9404,13 +9672,13 @@
       <c r="B27" t="s">
         <v>1068</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="15">
+        <v>7</v>
+      </c>
+      <c r="D27" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Nederpunk met humor. "Ik ben een feminist want ik hou ook van kleine tieten". Nou, daar gaat mijn ambitie richting mijn feminist-zijn.</v>
       </c>
       <c r="E27" s="1">
         <v>46207</v>
@@ -9483,13 +9751,13 @@
       <c r="B28" t="s">
         <v>1341</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="15">
+        <v>DJ.</v>
+      </c>
+      <c r="D28" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Vrouw, mexicaans, cumbia!</v>
       </c>
       <c r="E28" s="1">
         <v>46206</v>
@@ -9504,7 +9772,7 @@
         <v>1342</v>
       </c>
       <c r="I28" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="J28" t="s">
         <v>449</v>
@@ -9562,11 +9830,11 @@
       <c r="B29" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D29" s="15" t="str">
+      <c r="D29" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Aanstekelijke ernergie, zang niet altijd zuiver. Ooit gehoord - amper gezien want ik gok dat ze 1.50 m lang is ;-)-  in de Bossa Nova, nu op mainstage</v>
       </c>
@@ -9644,13 +9912,13 @@
       <c r="B30" t="s">
         <v>588</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="15">
+        <v>9</v>
+      </c>
+      <c r="D30" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Downtempo, moody, Burial, Boards Of Canada</v>
       </c>
       <c r="E30" s="1">
         <v>46207</v>
@@ -9726,11 +9994,11 @@
       <c r="B31" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Elk jaar is er een Franse dance live-act met een retro randje, en dit is 'm.</v>
       </c>
@@ -9808,13 +10076,13 @@
       <c r="B32" t="s">
         <v>1346</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="15">
+        <v>...</v>
+      </c>
+      <c r="D32" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Workshop</v>
       </c>
       <c r="E32" s="1">
         <v>46206</v>
@@ -9887,13 +10155,13 @@
       <c r="B33" t="s">
         <v>1374</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="15">
+        <v>...</v>
+      </c>
+      <c r="D33" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Kunst</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
@@ -9958,11 +10226,11 @@
       <c r="B34" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>10</v>
       </c>
-      <c r="D34" s="15" t="str">
+      <c r="D34" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Van de nieuwe plaat is niet iedereen fan (Bauke!) maar dit is toch niet te missen.</v>
       </c>
@@ -10040,13 +10308,13 @@
       <c r="B35" t="s">
         <v>481</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="15">
+        <v>6</v>
+      </c>
+      <c r="D35" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Lekkere slick muziek, jammer dat ie in het Brabants zingt</v>
       </c>
       <c r="E35" s="1">
         <v>46208</v>
@@ -10125,11 +10393,11 @@
       <c r="B36" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D36" s="15" t="str">
+      <c r="D36" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Pffff, de Staat van Ontbinding</v>
       </c>
@@ -10210,13 +10478,13 @@
       <c r="B37" t="s">
         <v>1074</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="15">
+        <v>7</v>
+      </c>
+      <c r="D37" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>De muziek is een stuk leuker dan de provinciale goth outfits en KISS make-up doen vermoeden. Clan Of Xymox.</v>
       </c>
       <c r="E37" s="1">
         <v>46207</v>
@@ -10292,13 +10560,13 @@
       <c r="B38" t="s">
         <v>336</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="15">
+        <v>8</v>
+      </c>
+      <c r="D38" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Op Lowlands gezien. Twee imposante broers. Luister "Shadowman"!</v>
       </c>
       <c r="E38" s="1">
         <v>46208</v>
@@ -10313,7 +10581,7 @@
         <v>111</v>
       </c>
       <c r="I38" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="J38" t="s">
         <v>337</v>
@@ -10377,13 +10645,13 @@
       <c r="B39" t="s">
         <v>1692</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="15">
+        <v>7</v>
+      </c>
+      <c r="D39" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Een beetje te jankerig soms, maar ook mooie Damien Rice-achtige melodieën.</v>
       </c>
       <c r="E39" s="1">
         <v>46206</v>
@@ -10459,11 +10727,11 @@
       <c r="B40" t="s">
         <v>344</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>10</v>
       </c>
-      <c r="D40" s="15" t="str">
+      <c r="D40" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Al gezien op Footprints 2025. Aanrader, dansbaar.</v>
       </c>
@@ -10544,11 +10812,11 @@
       <c r="B41" t="s">
         <v>1349</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D41" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -10565,7 +10833,7 @@
         <v>1342</v>
       </c>
       <c r="I41" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="J41" t="s">
         <v>1350</v>
@@ -10623,11 +10891,11 @@
       <c r="B42" t="s">
         <v>1553</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D42" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -10700,18 +10968,18 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B43" t="s">
         <v>1864</v>
       </c>
-      <c r="B43" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C43" s="12" t="str">
+      <c r="C43" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v/>
-      </c>
-      <c r="D43" s="15" t="str">
+        <v>DJ</v>
+      </c>
+      <c r="D43" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
         <v>46208</v>
@@ -10726,28 +10994,28 @@
         <v>111</v>
       </c>
       <c r="I43" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="J43" t="s">
         <v>74</v>
       </c>
       <c r="K43" t="s">
+        <v>1866</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1395</v>
+      </c>
+      <c r="M43" t="s">
         <v>1867</v>
       </c>
-      <c r="L43" t="s">
-        <v>1395</v>
-      </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P43" t="s">
         <v>1868</v>
-      </c>
-      <c r="N43" t="s">
-        <v>1395</v>
-      </c>
-      <c r="O43" t="s">
-        <v>1395</v>
-      </c>
-      <c r="P43" t="s">
-        <v>1869</v>
       </c>
       <c r="Q43">
         <v>7</v>
@@ -10762,16 +11030,16 @@
         <v>1395</v>
       </c>
       <c r="V43" t="s">
+        <v>1869</v>
+      </c>
+      <c r="W43" t="s">
         <v>1870</v>
       </c>
-      <c r="W43" t="s">
+      <c r="X43" t="s">
         <v>1871</v>
       </c>
-      <c r="X43" t="s">
+      <c r="Y43" t="s">
         <v>1872</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>1873</v>
       </c>
       <c r="Z43" t="s">
         <v>38</v>
@@ -10787,13 +11055,13 @@
       <c r="B44" t="s">
         <v>1265</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D44" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Shamaran is een mythisch figuur uit de Noord-Mesopotamische cultuur met de torso van een vrouw en het onderlichaam van twee slangen. Veel gezien in Mardin, Turkije de twee keer dat ik daar was. De DJ heeft "advanced rhythms, razor-sharp percussion, and raw textures"</v>
       </c>
       <c r="E44" s="1">
         <v>46207</v>
@@ -10805,7 +11073,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="H44" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I44" t="s">
         <v>1395</v>
@@ -10869,11 +11137,11 @@
       <c r="B45" t="s">
         <v>786</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D45" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -10951,11 +11219,11 @@
       <c r="B46" t="s">
         <v>793</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D46" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11033,13 +11301,13 @@
       <c r="B47" t="s">
         <v>1234</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="15">
+        <v>8</v>
+      </c>
+      <c r="D47" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Hun zien er uit als zwarte vrouw en spelen klassiek piano.</v>
       </c>
       <c r="E47" s="1">
         <v>46207</v>
@@ -11115,11 +11383,11 @@
       <c r="B48" t="s">
         <v>598</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D48" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11136,7 +11404,7 @@
         <v>547</v>
       </c>
       <c r="I48" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="J48" t="s">
         <v>162</v>
@@ -11197,11 +11465,11 @@
       <c r="B49" t="s">
         <v>605</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D49" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D49" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11279,11 +11547,11 @@
       <c r="B50" t="s">
         <v>1270</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D50" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11297,7 +11565,7 @@
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="H50" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I50" t="s">
         <v>675</v>
@@ -11361,11 +11629,11 @@
       <c r="B51" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D51" s="15" t="str">
+      <c r="D51" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Geen nieuw werk.</v>
       </c>
@@ -11446,11 +11714,11 @@
       <c r="B52" t="s">
         <v>614</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D52" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11467,7 +11735,7 @@
         <v>547</v>
       </c>
       <c r="I52" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="J52" t="s">
         <v>162</v>
@@ -11528,11 +11796,11 @@
       <c r="B53" t="s">
         <v>803</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D53" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D53" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11549,7 +11817,7 @@
         <v>743</v>
       </c>
       <c r="I53" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="J53" t="s">
         <v>281</v>
@@ -11610,13 +11878,13 @@
       <c r="B54" t="s">
         <v>934</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="15">
+        <v>10</v>
+      </c>
+      <c r="D54" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>a Belgian bassist known for her innovative approach to experimental and improvised music, blending elements of noise, jazz, and rock</v>
       </c>
       <c r="E54" s="1">
         <v>46207</v>
@@ -11692,11 +11960,11 @@
       <c r="B55" t="s">
         <v>621</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D55" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -11713,7 +11981,7 @@
         <v>547</v>
       </c>
       <c r="I55" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="J55" t="s">
         <v>162</v>
@@ -11774,13 +12042,13 @@
       <c r="B56" t="s">
         <v>1083</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D56" s="15">
+        <v>8</v>
+      </c>
+      <c r="D56" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Spannende moody post-punk. PJ Harvey.</v>
       </c>
       <c r="E56" s="1">
         <v>46206</v>
@@ -11853,11 +12121,11 @@
       <c r="B57" t="s">
         <v>26</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D57" s="15" t="str">
+      <c r="D57" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Tour van eerste album nog in Paradiso gezien, daarna nooit meer!</v>
       </c>
@@ -11935,11 +12203,11 @@
       <c r="B58" t="s">
         <v>353</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D58" s="15" t="str">
+      <c r="D58" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>De grungy Olivia Rodrigo</v>
       </c>
@@ -12020,11 +12288,11 @@
       <c r="B59" t="s">
         <v>362</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D59" s="15" t="str">
+      <c r="D59" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Nice harmonies, nice tunes</v>
       </c>
@@ -12105,13 +12373,13 @@
       <c r="B60" t="s">
         <v>1167</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="15">
+        <v>6</v>
+      </c>
+      <c r="D60" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Spinvis zonder de goede muziek.</v>
       </c>
       <c r="E60" s="1">
         <v>46207</v>
@@ -12184,13 +12452,13 @@
       <c r="B61" t="s">
         <v>808</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D61" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Niche: the only Afro-Indigenous Brazilian female DJ in Europe</v>
       </c>
       <c r="E61" s="1">
         <v>46207</v>
@@ -12205,7 +12473,7 @@
         <v>743</v>
       </c>
       <c r="I61" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="J61" t="s">
         <v>162</v>
@@ -12261,16 +12529,16 @@
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B62" t="s">
         <v>1395</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D62" s="15" t="str">
+      <c r="D62" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Zang klinkt als Bloc Party, saaie beats.</v>
       </c>
@@ -12320,16 +12588,16 @@
         <v>1395</v>
       </c>
       <c r="V62" t="s">
+        <v>1850</v>
+      </c>
+      <c r="W62" t="s">
         <v>1851</v>
       </c>
-      <c r="W62" t="s">
+      <c r="X62" t="s">
         <v>1852</v>
       </c>
-      <c r="X62" t="s">
+      <c r="Y62" t="s">
         <v>1853</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>1854</v>
       </c>
       <c r="Z62" t="s">
         <v>38</v>
@@ -12345,11 +12613,11 @@
       <c r="B63" t="s">
         <v>371</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D63" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -12430,13 +12698,13 @@
       <c r="B64" t="s">
         <v>1173</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="15">
+        <v>8</v>
+      </c>
+      <c r="D64" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Lekkere electo-pop, vijf vrouwen</v>
       </c>
       <c r="E64" s="1">
         <v>46206</v>
@@ -12512,13 +12780,13 @@
       <c r="B65" t="s">
         <v>1142</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="15">
+        <v>...</v>
+      </c>
+      <c r="D65" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Workshop</v>
       </c>
       <c r="E65" s="1">
         <v>46206</v>
@@ -12591,11 +12859,11 @@
       <c r="B66" t="s">
         <v>628</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D66" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -12612,7 +12880,7 @@
         <v>547</v>
       </c>
       <c r="I66" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="J66" t="s">
         <v>162</v>
@@ -12673,13 +12941,13 @@
       <c r="B67" t="s">
         <v>941</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="15">
+        <v>7</v>
+      </c>
+      <c r="D67" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>sometimes with hypnotic meditative sounds, other times with meticulously collected field recordings of humans and nature</v>
       </c>
       <c r="E67" s="1">
         <v>46207</v>
@@ -12752,11 +13020,11 @@
       <c r="B68" t="s">
         <v>945</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D68" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -12773,7 +13041,7 @@
         <v>923</v>
       </c>
       <c r="I68" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="J68" t="s">
         <v>162</v>
@@ -12831,11 +13099,11 @@
       <c r="B69" t="s">
         <v>1567</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D69" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -12852,7 +13120,7 @@
         <v>743</v>
       </c>
       <c r="I69" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="J69" t="s">
         <v>812</v>
@@ -12913,11 +13181,11 @@
       <c r="B70" t="s">
         <v>152</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D70" s="15" t="str">
+      <c r="D70" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Yo, yo, yo. Mid-tempo 90s beats. Eminem-ish frasing.</v>
       </c>
@@ -12995,13 +13263,13 @@
       <c r="B71" t="s">
         <v>949</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="15">
+        <v>6</v>
+      </c>
+      <c r="D71" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>"a haunting blend of neo-ambient, shoegaze, and lo-fi electronica"</v>
       </c>
       <c r="E71" s="1">
         <v>46208</v>
@@ -13016,7 +13284,7 @@
         <v>923</v>
       </c>
       <c r="I71" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="J71" t="s">
         <v>1395</v>
@@ -13074,11 +13342,11 @@
       <c r="B72" t="s">
         <v>631</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D72" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D72" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -13156,11 +13424,11 @@
       <c r="B73" t="s">
         <v>818</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D73" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -13238,13 +13506,13 @@
       <c r="B74" t="s">
         <v>1089</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="15">
+        <v>8</v>
+      </c>
+      <c r="D74" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Engelstalige electro-punk, lekker rommelig en vies</v>
       </c>
       <c r="E74" s="1">
         <v>46206</v>
@@ -13320,13 +13588,13 @@
       <c r="B75" t="s">
         <v>1095</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D75" s="15">
+        <v>8</v>
+      </c>
+      <c r="D75" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Lekkere shoegaze, en ik kan het weten want ik heb ze al in Club Pussycat gezien.</v>
       </c>
       <c r="E75" s="1">
         <v>46208</v>
@@ -13399,13 +13667,13 @@
       <c r="B76" t="s">
         <v>1656</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="15">
+        <v>9</v>
+      </c>
+      <c r="D76" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Hi-energy Korean electronic madness. Breakbeats. Acid.</v>
       </c>
       <c r="E76" s="1">
         <v>46207</v>
@@ -13420,7 +13688,7 @@
         <v>1062</v>
       </c>
       <c r="I76" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="J76" t="s">
         <v>1103</v>
@@ -13481,11 +13749,11 @@
       <c r="B77" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D77" s="15" t="str">
+      <c r="D77" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ik ga de juich recensies gewoon negeren, want het blijft nederhop in the end.</v>
       </c>
@@ -13566,11 +13834,11 @@
       <c r="B78" t="s">
         <v>381</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>9</v>
       </c>
-      <c r="D78" s="15" t="str">
+      <c r="D78" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Spannende Schotse folk-pop zanger. Jeff Buckley vergelijking gaat mank want Jacob heeft amper irritante maniertjes.</v>
       </c>
@@ -13651,13 +13919,13 @@
       <c r="B79" t="s">
         <v>954</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D79" s="15">
+        <v>...</v>
+      </c>
+      <c r="D79" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>field recordings</v>
       </c>
       <c r="E79" s="1">
         <v>46207</v>
@@ -13733,11 +14001,11 @@
       <c r="B80" t="s">
         <v>637</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D80" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D80" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -13754,7 +14022,7 @@
         <v>547</v>
       </c>
       <c r="I80" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="J80" t="s">
         <v>162</v>
@@ -13815,11 +14083,11 @@
       <c r="B81" t="s">
         <v>1737</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D81" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -13833,7 +14101,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="H81" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I81" t="s">
         <v>1277</v>
@@ -13897,13 +14165,13 @@
       <c r="B82" t="s">
         <v>168</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="15">
+        <v/>
+      </c>
+      <c r="D82" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E82" s="1">
         <v>46207</v>
@@ -13979,11 +14247,11 @@
       <c r="B83" t="s">
         <v>176</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D83" s="15" t="str">
+      <c r="D83" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Afvinken maar.</v>
       </c>
@@ -14061,11 +14329,11 @@
       <c r="B84" t="s">
         <v>185</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D84" s="15" t="str">
+      <c r="D84" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Vroeger zou ik Amy Winhouse-kloon hebben geschreven, tegenwoordig is dat Raye-kloon. Hopen dat ze niet net zo heel veel praat.</v>
       </c>
@@ -14143,13 +14411,13 @@
       <c r="B85" t="s">
         <v>1108</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="15">
+        <v>6</v>
+      </c>
+      <c r="D85" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Hiphop met reggaeton.</v>
       </c>
       <c r="E85" s="1">
         <v>46206</v>
@@ -14225,13 +14493,13 @@
       <c r="B86" t="s">
         <v>1114</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="15">
+        <v>8</v>
+      </c>
+      <c r="D86" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>"Stop Met Wenen" is een te gek nummer, rest ook leuk.</v>
       </c>
       <c r="E86" s="1">
         <v>46206</v>
@@ -14304,13 +14572,13 @@
       <c r="B87" t="s">
         <v>642</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="15">
+        <v>7</v>
+      </c>
+      <c r="D87" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>trumpeter creates cosmic deep house</v>
       </c>
       <c r="E87" s="1">
         <v>46206</v>
@@ -14386,11 +14654,11 @@
       <c r="B88" t="s">
         <v>826</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D88" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D88" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -14468,11 +14736,11 @@
       <c r="B89" t="s">
         <v>389</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D89" s="15" t="str">
+      <c r="D89" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Singer-songwriter, maar geen geknauw-zang. Klinkt sympathiek. Beetje te gezellig - op een gegeven moment ga je snakken naar een uithaal.</v>
       </c>
@@ -14550,13 +14818,13 @@
       <c r="B90" t="s">
         <v>1146</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D90" s="15">
+        <v>...</v>
+      </c>
+      <c r="D90" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>"ochtendperformance" van 13:45 - 14:30. "Marokkaanse muziekgenres"</v>
       </c>
       <c r="E90" s="1">
         <v>46208</v>
@@ -14632,13 +14900,13 @@
       <c r="B91" t="s">
         <v>835</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D91" s="15">
+        <v/>
+      </c>
+      <c r="D91" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E91" s="1">
         <v>46206</v>
@@ -14653,7 +14921,7 @@
         <v>743</v>
       </c>
       <c r="I91" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="J91" t="s">
         <v>812</v>
@@ -14714,11 +14982,11 @@
       <c r="B92" t="s">
         <v>1474</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D92" s="15" t="str">
+      <c r="D92" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Dit is de band die regenpijpen bespeelt met hun slippers!</v>
       </c>
@@ -14796,13 +15064,13 @@
       <c r="B93" t="s">
         <v>1357</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D93" s="15">
+        <v>...</v>
+      </c>
+      <c r="D93" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Knutselen</v>
       </c>
       <c r="E93" s="1">
         <v>46206</v>
@@ -14875,13 +15143,13 @@
       <c r="B94" t="s">
         <v>1151</v>
       </c>
-      <c r="C94" s="12">
+      <c r="C94" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D94" s="15">
+        <v>...</v>
+      </c>
+      <c r="D94" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Documentaires</v>
       </c>
       <c r="E94" s="1">
         <v>46208</v>
@@ -14954,13 +15222,13 @@
       <c r="B95" t="s">
         <v>1179</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D95" s="15">
+        <v>8</v>
+      </c>
+      <c r="D95" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Mooie vrouw maakt muziek "infused with Arabic influences". Frank gaat natuurlijk kijken.</v>
       </c>
       <c r="E95" s="1">
         <v>46206</v>
@@ -15036,13 +15304,13 @@
       <c r="B96" t="s">
         <v>958</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="15">
+        <v>6</v>
+      </c>
+      <c r="D96" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Chipmunks mompel rap over lofi beats</v>
       </c>
       <c r="E96" s="1">
         <v>46206</v>
@@ -15118,11 +15386,11 @@
       <c r="B97" t="s">
         <v>840</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D97" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D97" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -15139,7 +15407,7 @@
         <v>743</v>
       </c>
       <c r="I97" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="J97" t="s">
         <v>162</v>
@@ -15200,11 +15468,11 @@
       <c r="B98" t="s">
         <v>963</v>
       </c>
-      <c r="C98" s="12">
+      <c r="C98" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D98" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D98" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -15282,13 +15550,13 @@
       <c r="B99" t="s">
         <v>1158</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D99" s="15">
+        <v>...</v>
+      </c>
+      <c r="D99" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Kunst</v>
       </c>
       <c r="E99" s="1">
         <v>46023</v>
@@ -15364,11 +15632,11 @@
       <c r="B100" t="s">
         <v>1398</v>
       </c>
-      <c r="C100" s="12">
+      <c r="C100" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D100" s="15" t="str">
+      <c r="D100" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Lekkere stem, fijne beats</v>
       </c>
@@ -15446,13 +15714,13 @@
       <c r="B101" t="s">
         <v>1238</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D101" s="15">
+        <v>...</v>
+      </c>
+      <c r="D101" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Muziektheater?</v>
       </c>
       <c r="E101" s="1">
         <v>46208</v>
@@ -15525,11 +15793,11 @@
       <c r="B102" t="s">
         <v>82</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C102" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D102" s="15" t="str">
+      <c r="D102" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Je kunt ook zo laidback zijn dat je publiek in slaap valt.</v>
       </c>
@@ -15607,13 +15875,13 @@
       <c r="B103" t="s">
         <v>407</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D103" s="15">
+        <v>7</v>
+      </c>
+      <c r="D103" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Verstilde muziek</v>
       </c>
       <c r="E103" s="1">
         <v>46207</v>
@@ -15692,11 +15960,11 @@
       <c r="B104" t="s">
         <v>651</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D104" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D104" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -15774,11 +16042,11 @@
       <c r="B105" t="s">
         <v>658</v>
       </c>
-      <c r="C105" s="12">
+      <c r="C105" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D105" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D105" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -15856,13 +16124,13 @@
       <c r="B106" t="s">
         <v>1184</v>
       </c>
-      <c r="C106" s="12">
+      <c r="C106" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D106" s="15">
+        <v>7</v>
+      </c>
+      <c r="D106" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Nog meer muziek uit Afrika met huisvlijt instrumenten</v>
       </c>
       <c r="E106" s="1">
         <v>46207</v>
@@ -15941,13 +16209,13 @@
       <c r="B107" t="s">
         <v>1120</v>
       </c>
-      <c r="C107" s="12">
+      <c r="C107" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D107" s="15">
+        <v>...</v>
+      </c>
+      <c r="D107" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>support act for sisters-in-crime Pussy Riot</v>
       </c>
       <c r="E107" s="1">
         <v>46207</v>
@@ -16020,13 +16288,13 @@
       <c r="B108" t="s">
         <v>418</v>
       </c>
-      <c r="C108" s="12">
+      <c r="C108" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D108" s="15">
+        <v/>
+      </c>
+      <c r="D108" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E108" s="1">
         <v>46208</v>
@@ -16105,11 +16373,11 @@
       <c r="B109" t="s">
         <v>429</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D109" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D109" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -16190,11 +16458,11 @@
       <c r="B110" t="s">
         <v>970</v>
       </c>
-      <c r="C110" s="12">
+      <c r="C110" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D110" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D110" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -16272,11 +16540,11 @@
       <c r="B111" t="s">
         <v>977</v>
       </c>
-      <c r="C111" s="12">
+      <c r="C111" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D111" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D111" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -16354,13 +16622,13 @@
       <c r="B112" t="s">
         <v>848</v>
       </c>
-      <c r="C112" s="12">
+      <c r="C112" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D112" s="15">
+        <v>8</v>
+      </c>
+      <c r="D112" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Little Simz' bass player does a DJ set with "Afrohouse, batacuda, and Congolese soukous form the foundation for warm, soulful dance music from the global diaspora, drawing from jazz and old-school funk as well as modern dembow and kuduro"</v>
       </c>
       <c r="E112" s="1">
         <v>46207</v>
@@ -16375,7 +16643,7 @@
         <v>743</v>
       </c>
       <c r="I112" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="J112" t="s">
         <v>1395</v>
@@ -16436,11 +16704,11 @@
       <c r="B113" t="s">
         <v>665</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D113" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D113" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -16518,11 +16786,11 @@
       <c r="B114" t="s">
         <v>195</v>
       </c>
-      <c r="C114" s="12">
+      <c r="C114" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D114" s="15" t="str">
+      <c r="D114" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ik hou ook van The National</v>
       </c>
@@ -16600,11 +16868,11 @@
       <c r="B115" t="s">
         <v>1284</v>
       </c>
-      <c r="C115" s="12">
+      <c r="C115" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D115" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D115" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -16618,7 +16886,7 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="H115" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I115" t="s">
         <v>1285</v>
@@ -16682,13 +16950,13 @@
       <c r="B116" t="s">
         <v>982</v>
       </c>
-      <c r="C116" s="12">
+      <c r="C116" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D116" s="15">
+        <v>8</v>
+      </c>
+      <c r="D116" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Vrouw zingt (soms) over ambient en melancholische muziek. Jon Hopkins. "chill vibes"</v>
       </c>
       <c r="E116" s="1">
         <v>46206</v>
@@ -16764,11 +17032,11 @@
       <c r="B117" t="s">
         <v>447</v>
       </c>
-      <c r="C117" s="12">
+      <c r="C117" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D117" s="15" t="str">
+      <c r="D117" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Yacht-rock-smooth vocals, electronic beats. Zo karakterloos dat het AI-slop lijkt.</v>
       </c>
@@ -16849,11 +17117,11 @@
       <c r="B118" t="s">
         <v>456</v>
       </c>
-      <c r="C118" s="12">
+      <c r="C118" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D118" s="15" t="str">
+      <c r="D118" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v xml:space="preserve">Voor als je zin hebt in veilige genre-getrouwe Italo disco. Melig. Een gast-optreden van Sabrina zou een +1 zijn. </v>
       </c>
@@ -16931,11 +17199,11 @@
       <c r="B119" t="s">
         <v>738</v>
       </c>
-      <c r="C119" s="12">
+      <c r="C119" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D119" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D119" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17010,11 +17278,11 @@
       <c r="B120" t="s">
         <v>467</v>
       </c>
-      <c r="C120" s="12" t="str">
+      <c r="C120" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>DJ</v>
       </c>
-      <c r="D120" s="15">
+      <c r="D120" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17031,7 +17299,7 @@
         <v>111</v>
       </c>
       <c r="I120" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="J120" t="s">
         <v>162</v>
@@ -17095,13 +17363,13 @@
       <c r="B121" t="s">
         <v>1243</v>
       </c>
-      <c r="C121" s="12">
+      <c r="C121" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D121" s="15">
+        <v>7</v>
+      </c>
+      <c r="D121" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Strijkkwartet met muziek uit de vorige eeuw.</v>
       </c>
       <c r="E121" s="1">
         <v>46208</v>
@@ -17177,11 +17445,11 @@
       <c r="B122" t="s">
         <v>475</v>
       </c>
-      <c r="C122" s="12">
+      <c r="C122" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D122" s="15" t="str">
+      <c r="D122" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ik ben wel benieuwd</v>
       </c>
@@ -17259,11 +17527,11 @@
       <c r="B123" t="s">
         <v>1672</v>
       </c>
-      <c r="C123" s="12">
+      <c r="C123" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D123" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D123" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17333,16 +17601,16 @@
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B124" t="s">
         <v>1855</v>
       </c>
-      <c r="B124" t="s">
-        <v>1856</v>
-      </c>
-      <c r="C124" s="12" t="str">
+      <c r="C124" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v/>
       </c>
-      <c r="D124" s="15" t="str">
+      <c r="D124" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v/>
       </c>
@@ -17359,28 +17627,28 @@
         <v>111</v>
       </c>
       <c r="I124" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="J124" t="s">
         <v>62</v>
       </c>
       <c r="K124" t="s">
+        <v>1857</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1395</v>
+      </c>
+      <c r="M124" t="s">
         <v>1858</v>
       </c>
-      <c r="L124" t="s">
-        <v>1395</v>
-      </c>
-      <c r="M124" t="s">
+      <c r="N124" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P124" t="s">
         <v>1859</v>
-      </c>
-      <c r="N124" t="s">
-        <v>1395</v>
-      </c>
-      <c r="O124" t="s">
-        <v>1395</v>
-      </c>
-      <c r="P124" t="s">
-        <v>1860</v>
       </c>
       <c r="Q124">
         <v>7</v>
@@ -17395,16 +17663,16 @@
         <v>1395</v>
       </c>
       <c r="V124" t="s">
+        <v>1860</v>
+      </c>
+      <c r="W124" t="s">
         <v>1861</v>
       </c>
-      <c r="W124" t="s">
+      <c r="X124" t="s">
+        <v>1861</v>
+      </c>
+      <c r="Y124" t="s">
         <v>1862</v>
-      </c>
-      <c r="X124" t="s">
-        <v>1862</v>
-      </c>
-      <c r="Y124" t="s">
-        <v>1863</v>
       </c>
       <c r="Z124" t="s">
         <v>38</v>
@@ -17420,13 +17688,13 @@
       <c r="B125" t="s">
         <v>1194</v>
       </c>
-      <c r="C125" s="12">
+      <c r="C125" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D125" s="15">
+        <v>7</v>
+      </c>
+      <c r="D125" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Retro-soul met een beetje Norah Jones</v>
       </c>
       <c r="E125" s="1">
         <v>46208</v>
@@ -17502,11 +17770,11 @@
       <c r="B126" t="s">
         <v>491</v>
       </c>
-      <c r="C126" s="12">
+      <c r="C126" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D126" s="15">
+      <c r="D126" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17584,11 +17852,11 @@
       <c r="B127" t="s">
         <v>853</v>
       </c>
-      <c r="C127" s="12">
+      <c r="C127" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>5</v>
-      </c>
-      <c r="D127" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D127" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17666,13 +17934,13 @@
       <c r="B128" t="s">
         <v>991</v>
       </c>
-      <c r="C128" s="12">
+      <c r="C128" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D128" s="15">
+        <v>7</v>
+      </c>
+      <c r="D128" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Bring it on! "dissonant noise, ambient soundscapes, and intricate field recordings"</v>
       </c>
       <c r="E128" s="1">
         <v>46206</v>
@@ -17748,11 +18016,11 @@
       <c r="B129" t="s">
         <v>674</v>
       </c>
-      <c r="C129" s="12">
+      <c r="C129" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D129" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D129" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17830,11 +18098,11 @@
       <c r="B130" t="s">
         <v>1292</v>
       </c>
-      <c r="C130" s="12">
+      <c r="C130" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D130" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D130" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -17848,10 +18116,10 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="H130" t="s">
+        <v>1842</v>
+      </c>
+      <c r="I130" t="s">
         <v>1843</v>
-      </c>
-      <c r="I130" t="s">
-        <v>1844</v>
       </c>
       <c r="J130" t="s">
         <v>162</v>
@@ -17912,13 +18180,13 @@
       <c r="B131" t="s">
         <v>1001</v>
       </c>
-      <c r="C131" s="12">
+      <c r="C131" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D131" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D131" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v xml:space="preserve">Morocco-born DJ and curator [..] intersectional feminist </v>
       </c>
       <c r="E131" s="1">
         <v>46206</v>
@@ -17994,11 +18262,11 @@
       <c r="B132" t="s">
         <v>204</v>
       </c>
-      <c r="C132" s="12">
+      <c r="C132" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D132" s="15" t="str">
+      <c r="D132" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>De verplichte Franse electro-pop zangeres. Deze maakt wel heel lichtgewicht muziek.</v>
       </c>
@@ -18076,11 +18344,11 @@
       <c r="B133" t="s">
         <v>861</v>
       </c>
-      <c r="C133" s="12">
+      <c r="C133" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D133" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D133" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -18097,7 +18365,7 @@
         <v>743</v>
       </c>
       <c r="I133" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="J133" t="s">
         <v>162</v>
@@ -18155,13 +18423,13 @@
       <c r="B134" t="s">
         <v>1251</v>
       </c>
-      <c r="C134" s="12">
+      <c r="C134" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D134" s="15">
+        <v>...</v>
+      </c>
+      <c r="D134" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Theaterhater</v>
       </c>
       <c r="E134" s="1">
         <v>46206</v>
@@ -18234,11 +18502,11 @@
       <c r="B135" t="s">
         <v>1007</v>
       </c>
-      <c r="C135" s="12">
+      <c r="C135" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D135" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D135" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -18316,11 +18584,11 @@
       <c r="B136" t="s">
         <v>213</v>
       </c>
-      <c r="C136" s="12">
+      <c r="C136" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D136" s="15" t="str">
+      <c r="D136" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Alweer? Ben vorige keer weggelopen na 10 minuten.</v>
       </c>
@@ -18401,11 +18669,11 @@
       <c r="B137" t="s">
         <v>680</v>
       </c>
-      <c r="C137" s="12">
+      <c r="C137" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D137" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D137" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -18480,13 +18748,13 @@
       <c r="B138" t="s">
         <v>499</v>
       </c>
-      <c r="C138" s="12">
+      <c r="C138" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D138" s="15">
+        <v>7</v>
+      </c>
+      <c r="D138" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Vrouwen-punk</v>
       </c>
       <c r="E138" s="1">
         <v>46208</v>
@@ -18565,11 +18833,11 @@
       <c r="B139" t="s">
         <v>508</v>
       </c>
-      <c r="C139" s="12">
+      <c r="C139" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D139" s="15" t="str">
+      <c r="D139" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ik had ze al door Shazam getrokken toen ik het hoorde op The White Lotus soundtrack.</v>
       </c>
@@ -18650,11 +18918,11 @@
       <c r="B140" t="s">
         <v>685</v>
       </c>
-      <c r="C140" s="12">
+      <c r="C140" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D140" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D140" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -18732,11 +19000,11 @@
       <c r="B141" t="s">
         <v>518</v>
       </c>
-      <c r="C141" s="12">
+      <c r="C141" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D141" s="15" t="str">
+      <c r="D141" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ik moet de docu nog kijken. Classic electroclash.</v>
       </c>
@@ -18814,11 +19082,11 @@
       <c r="B142" t="s">
         <v>1016</v>
       </c>
-      <c r="C142" s="12">
+      <c r="C142" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D142" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D142" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -18835,7 +19103,7 @@
         <v>923</v>
       </c>
       <c r="I142" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="J142" t="s">
         <v>1017</v>
@@ -18893,13 +19161,13 @@
       <c r="B143" t="s">
         <v>1300</v>
       </c>
-      <c r="C143" s="12">
+      <c r="C143" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D143" s="15">
+        <v>7</v>
+      </c>
+      <c r="D143" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>multi-talent from London produces her own tracks</v>
       </c>
       <c r="E143" s="1">
         <v>46206</v>
@@ -18911,7 +19179,7 @@
         <v>0.94791666666666663</v>
       </c>
       <c r="H143" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I143" t="s">
         <v>1301</v>
@@ -18975,11 +19243,11 @@
       <c r="B144" t="s">
         <v>1370</v>
       </c>
-      <c r="C144" s="12">
+      <c r="C144" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D144" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D144" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -19057,11 +19325,11 @@
       <c r="B145" t="s">
         <v>1365</v>
       </c>
-      <c r="C145" s="12">
+      <c r="C145" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D145" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D145" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -19139,11 +19407,11 @@
       <c r="B146" t="s">
         <v>1361</v>
       </c>
-      <c r="C146" s="12">
+      <c r="C146" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>9</v>
       </c>
-      <c r="D146" s="15" t="str">
+      <c r="D146" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Vorig jaar lekker bij gedanst - beetje als St. Paul maar meer poppy.</v>
       </c>
@@ -19221,13 +19489,13 @@
       <c r="B147" t="s">
         <v>1025</v>
       </c>
-      <c r="C147" s="12">
+      <c r="C147" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D147" s="15">
+        <v>8</v>
+      </c>
+      <c r="D147" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Intrigerende titels. Spannende muziek. Met zang. Experimental. Electronic.</v>
       </c>
       <c r="E147" s="1">
         <v>46208</v>
@@ -19303,13 +19571,13 @@
       <c r="B148" t="s">
         <v>1202</v>
       </c>
-      <c r="C148" s="12">
+      <c r="C148" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D148" s="15">
+        <v>8</v>
+      </c>
+      <c r="D148" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v xml:space="preserve">Lekkere liedjes, lekkere stem. </v>
       </c>
       <c r="E148" s="1">
         <v>46208</v>
@@ -19375,20 +19643,20 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1033</v>
       </c>
       <c r="B149" t="s">
         <v>1034</v>
       </c>
-      <c r="C149" s="12">
+      <c r="C149" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D149" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D149" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>a masterful producer with an ear for unconventional textures and more introspective moments, turning his brilliant sets into a kind of meditative listening journey.</v>
       </c>
       <c r="E149" s="1">
         <v>46207</v>
@@ -19459,18 +19727,18 @@
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B150" t="s">
         <v>1883</v>
       </c>
-      <c r="B150" t="s">
-        <v>1884</v>
-      </c>
-      <c r="C150" s="12" t="str">
+      <c r="C150" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v/>
-      </c>
-      <c r="D150" s="15" t="str">
+        <v>...</v>
+      </c>
+      <c r="D150" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v/>
+        <v>Nederhop, denk ik</v>
       </c>
       <c r="E150" s="1">
         <v>46208</v>
@@ -19485,28 +19753,28 @@
         <v>408</v>
       </c>
       <c r="I150" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="J150" t="s">
         <v>162</v>
       </c>
       <c r="K150" t="s">
+        <v>1885</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1395</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O150" t="s">
+        <v>1395</v>
+      </c>
+      <c r="P150" t="s">
         <v>1886</v>
-      </c>
-      <c r="L150" t="s">
-        <v>1395</v>
-      </c>
-      <c r="M150" t="s">
-        <v>1859</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1395</v>
-      </c>
-      <c r="O150" t="s">
-        <v>1395</v>
-      </c>
-      <c r="P150" t="s">
-        <v>1887</v>
       </c>
       <c r="Q150">
         <v>6</v>
@@ -19524,16 +19792,16 @@
         <v>1395</v>
       </c>
       <c r="V150" t="s">
+        <v>1887</v>
+      </c>
+      <c r="W150" t="s">
         <v>1888</v>
       </c>
-      <c r="W150" t="s">
+      <c r="X150" t="s">
         <v>1889</v>
       </c>
-      <c r="X150" t="s">
+      <c r="Y150" t="s">
         <v>1890</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>1891</v>
       </c>
       <c r="Z150" t="s">
         <v>38</v>
@@ -19549,11 +19817,11 @@
       <c r="B151" t="s">
         <v>865</v>
       </c>
-      <c r="C151" s="12">
+      <c r="C151" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D151" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D151" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -19570,7 +19838,7 @@
         <v>743</v>
       </c>
       <c r="I151" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="J151" t="s">
         <v>162</v>
@@ -19628,13 +19896,13 @@
       <c r="B152" t="s">
         <v>1209</v>
       </c>
-      <c r="C152" s="12">
+      <c r="C152" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D152" s="15">
+        <v>8</v>
+      </c>
+      <c r="D152" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Lekkere grooves, leuke liedjes. On-Duits, meer Bee-Gees meets Whitest Boy Alive.</v>
       </c>
       <c r="E152" s="1">
         <v>46208</v>
@@ -19706,20 +19974,20 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>691</v>
       </c>
       <c r="B153" t="s">
         <v>692</v>
       </c>
-      <c r="C153" s="12">
+      <c r="C153" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D153" s="15">
+        <v>7</v>
+      </c>
+      <c r="D153" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>combining analog synth textures with complex rhythms to create atmospheric soundscapes</v>
       </c>
       <c r="E153" s="1">
         <v>46208</v>
@@ -19795,13 +20063,13 @@
       <c r="B154" t="s">
         <v>871</v>
       </c>
-      <c r="C154" s="12">
+      <c r="C154" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D154" s="15">
+        <v>7</v>
+      </c>
+      <c r="D154" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>a Brazilian live party with musicians gathered around a table</v>
       </c>
       <c r="E154" s="1">
         <v>46206</v>
@@ -19816,7 +20084,7 @@
         <v>743</v>
       </c>
       <c r="I154" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="J154" t="s">
         <v>162</v>
@@ -19874,11 +20142,11 @@
       <c r="B155" t="s">
         <v>1042</v>
       </c>
-      <c r="C155" s="12">
+      <c r="C155" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D155" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D155" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -19953,13 +20221,13 @@
       <c r="B156" t="s">
         <v>1309</v>
       </c>
-      <c r="C156" s="12">
+      <c r="C156" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D156" s="15">
+        <v>...</v>
+      </c>
+      <c r="D156" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>hyperpop</v>
       </c>
       <c r="E156" s="1">
         <v>46208</v>
@@ -19971,7 +20239,7 @@
         <v>0.94791666666666663</v>
       </c>
       <c r="H156" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I156" t="s">
         <v>1310</v>
@@ -20035,13 +20303,13 @@
       <c r="B157" t="s">
         <v>1607</v>
       </c>
-      <c r="C157" s="12">
+      <c r="C157" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D157" s="15">
+        <v>...</v>
+      </c>
+      <c r="D157" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Workshop</v>
       </c>
       <c r="E157" s="1">
         <v>46206</v>
@@ -20117,11 +20385,11 @@
       <c r="B158" t="s">
         <v>875</v>
       </c>
-      <c r="C158" s="12">
+      <c r="C158" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D158" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D158" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -20199,11 +20467,11 @@
       <c r="B159" t="s">
         <v>879</v>
       </c>
-      <c r="C159" s="12">
+      <c r="C159" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D159" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D159" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -20220,7 +20488,7 @@
         <v>743</v>
       </c>
       <c r="I159" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="J159" t="s">
         <v>162</v>
@@ -20281,11 +20549,11 @@
       <c r="B160" t="s">
         <v>222</v>
       </c>
-      <c r="C160" s="12">
+      <c r="C160" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D160" s="15" t="str">
+      <c r="D160" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Traditionele country, leuke zangeres.</v>
       </c>
@@ -20363,11 +20631,11 @@
       <c r="B161" t="s">
         <v>885</v>
       </c>
-      <c r="C161" s="12">
+      <c r="C161" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D161" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D161" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -20445,13 +20713,13 @@
       <c r="B162" t="s">
         <v>1685</v>
       </c>
-      <c r="C162" s="12">
+      <c r="C162" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D162" s="15">
+        <v>...</v>
+      </c>
+      <c r="D162" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Lezing</v>
       </c>
       <c r="E162" s="1">
         <v>46207</v>
@@ -20527,13 +20795,13 @@
       <c r="B163" t="s">
         <v>1217</v>
       </c>
-      <c r="C163" s="12">
+      <c r="C163" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D163" s="15">
+        <v/>
+      </c>
+      <c r="D163" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E163" s="1">
         <v>46208</v>
@@ -20548,7 +20816,7 @@
         <v>408</v>
       </c>
       <c r="I163" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="J163" t="s">
         <v>275</v>
@@ -20609,11 +20877,11 @@
       <c r="B164" t="s">
         <v>231</v>
       </c>
-      <c r="C164" s="12">
+      <c r="C164" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>5</v>
       </c>
-      <c r="D164" s="15" t="str">
+      <c r="D164" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Aanstellers</v>
       </c>
@@ -20694,11 +20962,11 @@
       <c r="B165" t="s">
         <v>1380</v>
       </c>
-      <c r="C165" s="12">
+      <c r="C165" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D165" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D165" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -20773,13 +21041,13 @@
       <c r="B166" t="s">
         <v>1224</v>
       </c>
-      <c r="C166" s="12">
+      <c r="C166" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D166" s="15">
+        <v>6</v>
+      </c>
+      <c r="D166" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Nederhop</v>
       </c>
       <c r="E166" s="1">
         <v>46207</v>
@@ -20855,13 +21123,13 @@
       <c r="B167" t="s">
         <v>1667</v>
       </c>
-      <c r="C167" s="12">
+      <c r="C167" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D167" s="15">
+        <v>6</v>
+      </c>
+      <c r="D167" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Nederhop</v>
       </c>
       <c r="E167" s="1">
         <v>46206</v>
@@ -20934,13 +21202,13 @@
       <c r="B168" t="s">
         <v>1391</v>
       </c>
-      <c r="C168" s="12">
+      <c r="C168" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D168" s="15">
+        <v>6</v>
+      </c>
+      <c r="D168" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Dutch rapper</v>
       </c>
       <c r="E168" s="1">
         <v>46208</v>
@@ -21016,13 +21284,13 @@
       <c r="B169" t="s">
         <v>260</v>
       </c>
-      <c r="C169" s="12">
+      <c r="C169" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D169" s="15">
+        <v>6</v>
+      </c>
+      <c r="D169" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Dutch rapper</v>
       </c>
       <c r="E169" s="1">
         <v>46208</v>
@@ -21095,13 +21363,13 @@
       <c r="B170" t="s">
         <v>255</v>
       </c>
-      <c r="C170" s="12">
+      <c r="C170" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D170" s="15">
+      <c r="D170" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Dutch rapper</v>
       </c>
       <c r="E170" s="1">
         <v>46206</v>
@@ -21174,13 +21442,13 @@
       <c r="B171" t="s">
         <v>1395</v>
       </c>
-      <c r="C171" s="12">
+      <c r="C171" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D171" s="15">
+        <v>...</v>
+      </c>
+      <c r="D171" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Wat zal het zijn? Ik heb geen voorspelling dit jaar.</v>
       </c>
       <c r="E171" s="1">
         <v>46207</v>
@@ -21253,13 +21521,13 @@
       <c r="B172" t="s">
         <v>1255</v>
       </c>
-      <c r="C172" s="12">
+      <c r="C172" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D172" s="15">
+        <v>...</v>
+      </c>
+      <c r="D172" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Performance</v>
       </c>
       <c r="E172" s="1">
         <v>46206</v>
@@ -21271,7 +21539,7 @@
         <v>0.875</v>
       </c>
       <c r="H172" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I172" t="s">
         <v>1395</v>
@@ -21332,11 +21600,11 @@
       <c r="B173" t="s">
         <v>91</v>
       </c>
-      <c r="C173" s="12">
+      <c r="C173" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D173" s="15" t="str">
+      <c r="D173" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Nu alweer terug! Tweede album valt een beetje tege.</v>
       </c>
@@ -21410,18 +21678,18 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>437</v>
       </c>
       <c r="B174" t="s">
         <v>438</v>
       </c>
-      <c r="C174" s="12">
+      <c r="C174" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D174" s="15" t="str">
+      <c r="D174" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v xml:space="preserve">Gezellige Irish-pub folk, niet de spannende Lankum dark-folk variant. "He went into a pub, and came out paralytic". </v>
       </c>
@@ -21502,13 +21770,13 @@
       <c r="B175" t="s">
         <v>1337</v>
       </c>
-      <c r="C175" s="12">
+      <c r="C175" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D175" s="15">
+        <v>...</v>
+      </c>
+      <c r="D175" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Workshop</v>
       </c>
       <c r="E175" s="1">
         <v>46206</v>
@@ -21520,7 +21788,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="H175" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I175" t="s">
         <v>886</v>
@@ -21581,11 +21849,11 @@
       <c r="B176" t="s">
         <v>49</v>
       </c>
-      <c r="C176" s="12">
+      <c r="C176" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>7</v>
       </c>
-      <c r="D176" s="15" t="str">
+      <c r="D176" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Twee punten aftrek vanwege het touren zonder nieuw album.</v>
       </c>
@@ -21666,11 +21934,11 @@
       <c r="B177" t="s">
         <v>248</v>
       </c>
-      <c r="C177" s="12">
+      <c r="C177" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D177" s="15" t="str">
+      <c r="D177" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Yes, it's another retro soul band, but the great Curtis Mayfield-ish vocals, Marvin Gay-ish arrangements, great drums sounds and  nice horn arrangements make me curious to see how they're live.</v>
       </c>
@@ -21751,11 +22019,11 @@
       <c r="B178" t="s">
         <v>891</v>
       </c>
-      <c r="C178" s="12">
+      <c r="C178" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D178" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D178" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -21833,11 +22101,11 @@
       <c r="B179" t="s">
         <v>1317</v>
       </c>
-      <c r="C179" s="12">
+      <c r="C179" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D179" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D179" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -21851,13 +22119,13 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H179" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I179" t="s">
+        <v>1844</v>
+      </c>
+      <c r="J179" t="s">
         <v>1845</v>
-      </c>
-      <c r="J179" t="s">
-        <v>1846</v>
       </c>
       <c r="K179" t="s">
         <v>1741</v>
@@ -21915,11 +22183,11 @@
       <c r="B180" t="s">
         <v>700</v>
       </c>
-      <c r="C180" s="12">
+      <c r="C180" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D180" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D180" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -21997,13 +22265,13 @@
       <c r="B181" t="s">
         <v>266</v>
       </c>
-      <c r="C181" s="12">
+      <c r="C181" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D181" s="15" t="str">
+      <c r="D181" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>Ik vind de plaat leuk (en hem 'm op vinyl).</v>
+        <v>Ik vind de plaat leuk (en heb 'm op vinyl).</v>
       </c>
       <c r="E181" s="1">
         <v>46206</v>
@@ -22082,11 +22350,11 @@
       <c r="B182" t="s">
         <v>1050</v>
       </c>
-      <c r="C182" s="12">
+      <c r="C182" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D182" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D182" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -22164,13 +22432,13 @@
       <c r="B183" t="s">
         <v>898</v>
       </c>
-      <c r="C183" s="12">
+      <c r="C183" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D183" s="15">
+        <v>9</v>
+      </c>
+      <c r="D183" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Woman from Milan plays a "unique fusion of old-school Arabic tunes and global club sounds</v>
       </c>
       <c r="E183" s="1">
         <v>46208</v>
@@ -22243,11 +22511,11 @@
       <c r="B184" t="s">
         <v>1321</v>
       </c>
-      <c r="C184" s="12">
+      <c r="C184" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D184" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D184" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -22261,7 +22529,7 @@
         <v>0.125</v>
       </c>
       <c r="H184" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I184" t="s">
         <v>1322</v>
@@ -22325,11 +22593,11 @@
       <c r="B185" t="s">
         <v>527</v>
       </c>
-      <c r="C185" s="12">
+      <c r="C185" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D185" s="15" t="str">
+      <c r="D185" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>ADHD electronica met hyper-poppy versnipperde smurfen-zang</v>
       </c>
@@ -22410,11 +22678,11 @@
       <c r="B186" t="s">
         <v>705</v>
       </c>
-      <c r="C186" s="12">
+      <c r="C186" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D186" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D186" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -22492,13 +22760,13 @@
       <c r="B187" t="s">
         <v>1388</v>
       </c>
-      <c r="C187" s="12">
+      <c r="C187" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D187" s="15">
+        <v>...</v>
+      </c>
+      <c r="D187" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>camera obscura</v>
       </c>
       <c r="E187" s="1"/>
       <c r="F187" s="2"/>
@@ -22563,13 +22831,13 @@
       <c r="B188" t="s">
         <v>1131</v>
       </c>
-      <c r="C188" s="12">
+      <c r="C188" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D188" s="15">
+        <v>7</v>
+      </c>
+      <c r="D188" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>High-speed electroclash en punk. Klinkt een beetje geposeerd.</v>
       </c>
       <c r="E188" s="1">
         <v>46208</v>
@@ -22645,11 +22913,11 @@
       <c r="B189" t="s">
         <v>711</v>
       </c>
-      <c r="C189" s="12">
+      <c r="C189" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D189" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D189" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -22720,20 +22988,20 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>717</v>
       </c>
       <c r="B190" t="s">
         <v>718</v>
       </c>
-      <c r="C190" s="12">
+      <c r="C190" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D190" s="15">
+        <v>8</v>
+      </c>
+      <c r="D190" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Downtempo, moody, vocal samples, spoken word snippets, Boards Of Canada, ja ongeveer net zo als Croatian Amor</v>
       </c>
       <c r="E190" s="1">
         <v>46207</v>
@@ -22809,11 +23077,11 @@
       <c r="B191" t="s">
         <v>725</v>
       </c>
-      <c r="C191" s="12">
+      <c r="C191" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D191" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D191" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -22830,7 +23098,7 @@
         <v>547</v>
       </c>
       <c r="I191" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="J191" t="s">
         <v>726</v>
@@ -22891,13 +23159,13 @@
       <c r="B192" t="s">
         <v>1056</v>
       </c>
-      <c r="C192" s="12">
+      <c r="C192" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D192" s="15">
+        <v>...</v>
+      </c>
+      <c r="D192" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Performance</v>
       </c>
       <c r="E192" s="1">
         <v>46208</v>
@@ -22970,11 +23238,11 @@
       <c r="B193" t="s">
         <v>536</v>
       </c>
-      <c r="C193" s="12">
+      <c r="C193" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>8</v>
       </c>
-      <c r="D193" s="15" t="str">
+      <c r="D193" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Manchester! Goede energie. Bij Jools Holland gezien dat de zingende bassiste mooi kan schreeuwen.</v>
       </c>
@@ -23055,13 +23323,13 @@
       <c r="B194" t="s">
         <v>1384</v>
       </c>
-      <c r="C194" s="12">
+      <c r="C194" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D194" s="15">
+        <v>...</v>
+      </c>
+      <c r="D194" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Workshop</v>
       </c>
       <c r="E194" s="1">
         <v>46206</v>
@@ -23134,11 +23402,11 @@
       <c r="B195" t="s">
         <v>1330</v>
       </c>
-      <c r="C195" s="12">
+      <c r="C195" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D195" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D195" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -23152,10 +23420,10 @@
         <v>0.125</v>
       </c>
       <c r="H195" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I195" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="J195" t="s">
         <v>162</v>
@@ -23216,13 +23484,13 @@
       <c r="B196" t="s">
         <v>902</v>
       </c>
-      <c r="C196" s="12">
+      <c r="C196" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D196" s="15">
+        <v xml:space="preserve">DJ </v>
+      </c>
+      <c r="D196" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Nepo-baby. Yucky is de zoon van Chuckie.</v>
       </c>
       <c r="E196" s="1">
         <v>46209</v>
@@ -23237,7 +23505,7 @@
         <v>743</v>
       </c>
       <c r="I196" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="J196" t="s">
         <v>162</v>
@@ -23298,11 +23566,11 @@
       <c r="B197" t="s">
         <v>905</v>
       </c>
-      <c r="C197" s="12">
+      <c r="C197" s="9" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D197" s="15">
+        <v>DJ</v>
+      </c>
+      <c r="D197" s="12">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>0</v>
       </c>
@@ -23319,7 +23587,7 @@
         <v>743</v>
       </c>
       <c r="I197" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="J197" t="s">
         <v>162</v>
@@ -23380,13 +23648,13 @@
       <c r="B198" t="s">
         <v>909</v>
       </c>
-      <c r="C198" s="12">
+      <c r="C198" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D198" s="15">
+        <v>7</v>
+      </c>
+      <c r="D198" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Contemporary Classical + Experimental</v>
       </c>
       <c r="E198" s="1">
         <v>46208</v>
@@ -23462,13 +23730,13 @@
       <c r="B199" t="s">
         <v>731</v>
       </c>
-      <c r="C199" s="12">
+      <c r="C199" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
-        <v>0</v>
-      </c>
-      <c r="D199" s="15">
+        <v>8</v>
+      </c>
+      <c r="D199" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
-        <v>0</v>
+        <v>Drum-'n-bass</v>
       </c>
       <c r="E199" s="1">
         <v>46207</v>
@@ -23541,11 +23809,11 @@
       <c r="B200" t="s">
         <v>280</v>
       </c>
-      <c r="C200" s="12">
+      <c r="C200" s="9">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Rating], "",)</f>
         <v>6</v>
       </c>
-      <c r="D200" s="15" t="str">
+      <c r="D200" s="12" t="str">
         <f>_xlfn.XLOOKUP(_2026[[#This Row],[Artist]], Table3[Artist], Table3[Notes], "",)</f>
         <v>Ook Belgische nederhop is saai.</v>
       </c>
@@ -23626,12 +23894,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F13413F-1C70-4AC9-A96B-C6378B266FA5}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C196"/>
+  <sheetPr codeName="Sheet2">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="7"/>
+    <col min="2" max="2" width="13.28515625" style="7" customWidth="1"/>
     <col min="3" max="3" width="74" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23648,232 +23918,278 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>397</v>
+        <v>1444</v>
       </c>
       <c r="B2" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1776</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1444</v>
+        <v>1228</v>
       </c>
       <c r="B3" s="8">
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1806</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B4" s="8">
-        <v>7</v>
+        <v>741</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1899</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1780</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="B5" s="8"/>
+        <v>1258</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="5"/>
+        <v>98</v>
+      </c>
+      <c r="B6" s="8">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1801</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="8">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>1802</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
+        <v>109</v>
+      </c>
+      <c r="B8" s="8">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1891</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B9" s="8">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1892</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B10" s="8">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1779</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="B11" s="8"/>
+        <v>554</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="5"/>
+        <v>297</v>
+      </c>
+      <c r="B12" s="8">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1893</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B13" s="8">
-        <v>7</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1894</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
+        <v>308</v>
+      </c>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1898</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="B15" s="8">
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1899</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>562</v>
       </c>
       <c r="B16" s="8">
         <v>8</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1793</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="B17" s="8"/>
+        <v>921</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="5"/>
+        <v>1060</v>
+      </c>
+      <c r="B18" s="8">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1932</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B19" s="8"/>
+        <v>765</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="5"/>
+        <v>571</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1927</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="B21" s="8"/>
+        <v>771</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="B22" s="8"/>
+        <v>929</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
+        <v>317</v>
+      </c>
+      <c r="B23" s="8">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1807</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B24" s="8">
-        <v>7</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>1808</v>
-      </c>
+      <c r="A24" s="13" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C24" s="15"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="8">
+        <v>7</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>1067</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="8">
+        <v>7</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>1936</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="8" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1958</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -23890,8 +24206,12 @@
       <c r="A30" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="8">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1924</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -23908,15 +24228,23 @@
       <c r="A32" s="4" t="s">
         <v>1345</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="5"/>
+      <c r="B32" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>1764</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>1971</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -23933,8 +24261,12 @@
       <c r="A35" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="8">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1901</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -23944,29 +24276,41 @@
         <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="8">
+        <v>7</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>1938</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="5"/>
+      <c r="B38" s="8">
+        <v>8</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>1903</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>1161</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="5"/>
+      <c r="B39" s="8">
+        <v>7</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>1908</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -23983,538 +24327,714 @@
       <c r="A41" s="4" t="s">
         <v>1348</v>
       </c>
-      <c r="B41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="B42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="13" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C43" s="15"/>
+    </row>
+    <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="5"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="5"/>
+      <c r="B44" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>1960</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>792</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>785</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>792</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C46" s="5"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="5"/>
+        <v>1233</v>
+      </c>
+      <c r="B47" s="8">
+        <v>8</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>1910</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B48" s="8"/>
+        <v>597</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B49" s="8"/>
+        <v>604</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="8">
-        <v>7</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>1783</v>
-      </c>
+        <v>1269</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="B51" s="8">
+        <v>7</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>1783</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="B52" s="8"/>
+        <v>613</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="5"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="5"/>
+      <c r="B54" s="8">
+        <v>10</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>1951</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B55" s="8"/>
+        <v>620</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>25</v>
+        <v>1082</v>
       </c>
       <c r="B56" s="8">
         <v>8</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>1796</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>352</v>
+        <v>25</v>
       </c>
       <c r="B57" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>1813</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B58" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>1895</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="5"/>
+        <v>361</v>
+      </c>
+      <c r="B59" s="8">
+        <v>8</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>1894</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="5"/>
+        <v>1166</v>
+      </c>
+      <c r="B60" s="8">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>1912</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="5"/>
+        <v>807</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>1965</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="5"/>
+        <v>1849</v>
+      </c>
+      <c r="B62" s="8">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>1896</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B63" s="8"/>
+        <v>370</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C63" s="5"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="5"/>
+        <v>1172</v>
+      </c>
+      <c r="B64" s="8">
+        <v>8</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>1909</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="5"/>
+        <v>1141</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="B66" s="8"/>
+        <v>627</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C66" s="5"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="5"/>
+        <v>1614</v>
+      </c>
+      <c r="B67" s="8">
+        <v>7</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>1950</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B68" s="8">
-        <v>6</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>1807</v>
-      </c>
+        <v>944</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="B69" s="8"/>
+        <v>811</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C69" s="5"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>1508</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="5"/>
+        <v>151</v>
+      </c>
+      <c r="B70" s="8">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>1806</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="5"/>
+        <v>948</v>
+      </c>
+      <c r="B71" s="8">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>1953</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B72" s="8"/>
+        <v>1508</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C72" s="5"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B73" s="8"/>
+        <v>817</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C73" s="5"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="5"/>
+        <v>1088</v>
+      </c>
+      <c r="B74" s="8">
+        <v>8</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>1928</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>159</v>
+        <v>1094</v>
       </c>
       <c r="B75" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>380</v>
+        <v>1102</v>
       </c>
       <c r="B76" s="8">
         <v>9</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>1811</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="5"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="B77" s="8">
+        <v>6</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="5"/>
+        <v>380</v>
+      </c>
+      <c r="B78" s="8">
+        <v>9</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>1810</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="5"/>
+        <v>953</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1948</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="8"/>
+        <v>636</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C81" s="5"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B82" s="8">
         <v>7</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
+      <c r="C82" s="5" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B83" s="8">
         <v>8</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="5"/>
+      <c r="C83" s="5" t="s">
+        <v>1811</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="5"/>
+        <v>1107</v>
+      </c>
+      <c r="B84" s="8">
+        <v>6</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>1930</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="5"/>
+        <v>1113</v>
+      </c>
+      <c r="B85" s="8">
+        <v>8</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>1931</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="B86" s="8">
+        <v>7</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="5"/>
-    </row>
-    <row r="87" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
+      <c r="B87" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C87" s="5"/>
+    </row>
+    <row r="88" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B88" s="8">
         <v>7</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="5"/>
+      <c r="C88" s="5" t="s">
+        <v>1814</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="B89" s="8"/>
-      <c r="C89" s="5"/>
+        <v>1145</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>1941</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="B90" s="8">
+        <v>8</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>1776</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="5"/>
+        <v>1356</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>1955</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
         <v>1700</v>
       </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="5"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="5"/>
+      <c r="B93" s="8">
+        <v>8</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>1906</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>839</v>
-      </c>
-      <c r="B94" s="8"/>
-      <c r="C94" s="5"/>
+        <v>957</v>
+      </c>
+      <c r="B94" s="8">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1946</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="B95" s="8"/>
+        <v>839</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B96" s="8"/>
+        <v>962</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B97" s="8">
-        <v>8</v>
+        <v>1157</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>1973</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>1784</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>1719</v>
-      </c>
-      <c r="B98" s="8"/>
-      <c r="C98" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="B98" s="8">
+        <v>8</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>1784</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B99" s="8">
-        <v>7</v>
+        <v>1719</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>1973</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>1795</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>1475</v>
-      </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="B100" s="8">
+        <v>7</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>1795</v>
+      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="5"/>
+        <v>1475</v>
+      </c>
+      <c r="B101" s="8">
+        <v>7</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>1911</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="B102" s="8"/>
+        <v>650</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B103" s="8"/>
+        <v>657</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="5"/>
+        <v>1183</v>
+      </c>
+      <c r="B104" s="8">
+        <v>7</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>1913</v>
+      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="B105" s="8"/>
-      <c r="C105" s="5"/>
+        <v>1119</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1935</v>
+      </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B106" s="8"/>
+      <c r="B106" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="B107" s="8"/>
+      <c r="B107" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="B108" s="8"/>
+      <c r="B108" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C108" s="5"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="B109" s="8"/>
-      <c r="C109" s="5"/>
+      <c r="B109" s="8">
+        <v>8</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>1964</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="B110" s="8"/>
+      <c r="B110" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -24525,22 +25045,28 @@
         <v>8</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>1283</v>
       </c>
-      <c r="B112" s="8"/>
+      <c r="B112" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C112" s="5"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="B113" s="8"/>
-      <c r="C113" s="5"/>
+      <c r="B113" s="8">
+        <v>8</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>1944</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -24550,7 +25076,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -24561,14 +25087,16 @@
         <v>7</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="B116" s="8"/>
+      <c r="B116" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -24576,7 +25104,7 @@
         <v>466</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="C117" s="5"/>
     </row>
@@ -24584,8 +25112,12 @@
       <c r="A118" s="4" t="s">
         <v>1242</v>
       </c>
-      <c r="B118" s="8"/>
-      <c r="C118" s="5"/>
+      <c r="B118" s="8">
+        <v>7</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>1915</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
@@ -24602,15 +25134,21 @@
       <c r="A120" s="4" t="s">
         <v>1139</v>
       </c>
-      <c r="B120" s="8"/>
+      <c r="B120" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C120" s="5"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>1193</v>
       </c>
-      <c r="B121" s="8"/>
-      <c r="C121" s="5"/>
+      <c r="B121" s="8">
+        <v>7</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>1917</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
@@ -24625,38 +25163,50 @@
       <c r="A123" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="B123" s="8">
-        <v>5</v>
+      <c r="B123" s="8" t="s">
+        <v>1899</v>
       </c>
       <c r="C123" s="5"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="B124" s="8"/>
-      <c r="C124" s="5"/>
+      <c r="B124" s="8">
+        <v>7</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>1945</v>
+      </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>1519</v>
       </c>
-      <c r="B125" s="8"/>
+      <c r="B125" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>1291</v>
       </c>
-      <c r="B126" s="8"/>
+      <c r="B126" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>1000</v>
       </c>
-      <c r="B127" s="8"/>
-      <c r="C127" s="5"/>
+      <c r="B127" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>1947</v>
+      </c>
     </row>
     <row r="128" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
@@ -24666,28 +25216,36 @@
         <v>7</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="B129" s="8"/>
+      <c r="B129" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="B130" s="8"/>
-      <c r="C130" s="5"/>
+      <c r="B130" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>1907</v>
+      </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="B131" s="8"/>
+      <c r="B131" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -24698,22 +25256,28 @@
         <v>6</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="B133" s="8"/>
+      <c r="B133" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B134" s="8"/>
-      <c r="C134" s="5"/>
+      <c r="B134" s="8">
+        <v>7</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>1904</v>
+      </c>
     </row>
     <row r="135" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
@@ -24723,14 +25287,16 @@
         <v>8</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="B136" s="8"/>
+      <c r="B136" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -24748,28 +25314,38 @@
       <c r="A138" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="B138" s="8"/>
+      <c r="B138" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>1299</v>
       </c>
-      <c r="B139" s="8"/>
-      <c r="C139" s="5"/>
+      <c r="B139" s="8">
+        <v>7</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>1959</v>
+      </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>1369</v>
       </c>
-      <c r="B140" s="8"/>
+      <c r="B140" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>1364</v>
       </c>
-      <c r="B141" s="8"/>
+      <c r="B141" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -24780,124 +25356,174 @@
         <v>9</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="B143" s="8"/>
-      <c r="C143" s="5"/>
+      <c r="B143" s="8">
+        <v>8</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>1954</v>
+      </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>1201</v>
       </c>
-      <c r="B144" s="8"/>
-      <c r="C144" s="5"/>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="8">
+        <v>8</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>1033</v>
       </c>
-      <c r="B145" s="8"/>
-      <c r="C145" s="5"/>
+      <c r="B145" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>1949</v>
+      </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
-        <v>864</v>
-      </c>
-      <c r="B146" s="8"/>
-      <c r="C146" s="5"/>
+      <c r="A146" s="13" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C146" s="15" t="s">
+        <v>1918</v>
+      </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B147" s="8"/>
+        <v>864</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B148" s="8">
+        <v>8</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="B148" s="8"/>
-      <c r="C148" s="5"/>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="B149" s="8"/>
-      <c r="C149" s="5"/>
+      <c r="B149" s="8">
+        <v>7</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>1926</v>
+      </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B150" s="8"/>
-      <c r="C150" s="5"/>
+        <v>870</v>
+      </c>
+      <c r="B150" s="8">
+        <v>7</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1962</v>
+      </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B151" s="8"/>
+        <v>1041</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="B152" s="8"/>
-      <c r="C152" s="5"/>
+        <v>1308</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>1961</v>
+      </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B153" s="8"/>
-      <c r="C153" s="5"/>
+        <v>917</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="B154" s="8"/>
+        <v>1586</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B155" s="8">
-        <v>7</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>1787</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="B156" s="8"/>
-      <c r="C156" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="B156" s="8">
+        <v>7</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>1787</v>
+      </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B157" s="8"/>
+        <v>884</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>1216</v>
-      </c>
-      <c r="B158" s="8"/>
-      <c r="C158" s="5"/>
+        <v>1154</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>1933</v>
+      </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
@@ -24914,36 +25540,54 @@
       <c r="A160" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="B160" s="8"/>
+      <c r="B160" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>1223</v>
       </c>
-      <c r="B161" s="8"/>
-      <c r="C161" s="5"/>
+      <c r="B161" s="8">
+        <v>6</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>1914</v>
+      </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>1126</v>
       </c>
-      <c r="B162" s="8"/>
-      <c r="C162" s="5"/>
+      <c r="B162" s="8">
+        <v>6</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>1914</v>
+      </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="B163" s="8"/>
-      <c r="C163" s="5"/>
+      <c r="B163" s="8">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1905</v>
+      </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B164" s="8"/>
-      <c r="C164" s="5"/>
+      <c r="B164" s="8">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1905</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
@@ -24952,21 +25596,31 @@
       <c r="B165" s="8">
         <v>6</v>
       </c>
-      <c r="C165" s="5"/>
+      <c r="C165" t="s">
+        <v>1905</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>1137</v>
       </c>
-      <c r="B166" s="8"/>
-      <c r="C166" s="5"/>
+      <c r="B166" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>1937</v>
+      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="B167" s="8"/>
-      <c r="C167" s="5"/>
+      <c r="B167" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>1952</v>
+      </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
@@ -24987,15 +25641,19 @@
         <v>6</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>1336</v>
       </c>
-      <c r="B170" s="8"/>
-      <c r="C170" s="5"/>
+      <c r="B170" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
@@ -25023,21 +25681,27 @@
       <c r="A173" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="B173" s="8"/>
+      <c r="B173" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>1316</v>
       </c>
-      <c r="B174" s="8"/>
+      <c r="B174" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="B175" s="8"/>
+      <c r="B175" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -25048,28 +25712,36 @@
         <v>8</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1799</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>1049</v>
       </c>
-      <c r="B177" s="8"/>
+      <c r="B177" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C177" s="5"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="B178" s="8"/>
-      <c r="C178" s="5"/>
+      <c r="B178" s="8">
+        <v>9</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>1966</v>
+      </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>1320</v>
       </c>
-      <c r="B179" s="8"/>
+      <c r="B179" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C179" s="5"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -25080,59 +25752,81 @@
         <v>8</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="B181" s="8"/>
+      <c r="B181" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>1387</v>
       </c>
-      <c r="B182" s="8"/>
-      <c r="C182" s="5"/>
+      <c r="B182" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1972</v>
+      </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="B183" s="8"/>
-      <c r="C183" s="5"/>
+      <c r="B183" s="8">
+        <v>7</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>1943</v>
+      </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="B184" s="8"/>
+      <c r="B184" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C184" s="5"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="B185" s="8"/>
-      <c r="C185" s="5"/>
+      <c r="B185" s="8">
+        <v>8</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>1925</v>
+      </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B186" s="8"/>
+      <c r="B186" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C186" s="5"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="B187" s="8"/>
-      <c r="C187" s="5"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B187" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>535</v>
       </c>
@@ -25140,50 +25834,70 @@
         <v>8</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>1383</v>
       </c>
-      <c r="B189" s="8"/>
-      <c r="C189" s="5"/>
+      <c r="B189" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>1329</v>
       </c>
-      <c r="B190" s="8"/>
+      <c r="B190" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="B191" s="8"/>
-      <c r="C191" s="5"/>
+      <c r="B191" s="8" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>1970</v>
+      </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="6" t="s">
         <v>1602</v>
       </c>
-      <c r="B192" s="8"/>
+      <c r="B192" s="8" t="s">
+        <v>1899</v>
+      </c>
       <c r="C192" s="5"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="s">
+      <c r="A193" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="B193" s="8"/>
-      <c r="C193" s="5"/>
+      <c r="B193" s="8">
+        <v>7</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>1967</v>
+      </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="6" t="s">
         <v>730</v>
       </c>
-      <c r="B194" s="8"/>
-      <c r="C194" s="5"/>
+      <c r="B194" s="8">
+        <v>8</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>1923</v>
+      </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
@@ -25196,21 +25910,46 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="9" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B196" s="10">
-        <v>6</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>1897</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B195">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
